--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.94175362647861</v>
+        <v>5.028034964302774</v>
       </c>
       <c r="D2" t="n">
-        <v>30.10568939069614</v>
+        <v>4.892174525988123</v>
       </c>
       <c r="E2" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F2" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.77538764502371</v>
+        <v>7.276000492316353</v>
       </c>
       <c r="D3" t="n">
-        <v>43.76770440612813</v>
+        <v>7.112251965995821</v>
       </c>
       <c r="E3" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F3" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.83030589064449</v>
+        <v>8.74742470722973</v>
       </c>
       <c r="D4" t="n">
-        <v>52.80033796626498</v>
+        <v>8.580054919518059</v>
       </c>
       <c r="E4" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F4" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.52180867508526</v>
+        <v>3.009793909701356</v>
       </c>
       <c r="D5" t="n">
-        <v>19.57922232595278</v>
+        <v>3.181623627967328</v>
       </c>
       <c r="E5" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F5" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.37387057132948</v>
+        <v>5.098253967841041</v>
       </c>
       <c r="D6" t="n">
-        <v>27.68686027488547</v>
+        <v>4.499114794668889</v>
       </c>
       <c r="E6" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F6" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.29858979672423</v>
+        <v>8.011020841967687</v>
       </c>
       <c r="D7" t="n">
-        <v>12.53993620398445</v>
+        <v>2.037739633147474</v>
       </c>
       <c r="E7" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F7" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.73936740222958</v>
+        <v>4.670147202862307</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03841917109821</v>
+        <v>4.556243115303459</v>
       </c>
       <c r="E8" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F8" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.80200040566128</v>
+        <v>3.542825065919958</v>
       </c>
       <c r="D9" t="n">
-        <v>20.5275839566547</v>
+        <v>3.335732392956388</v>
       </c>
       <c r="E9" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F9" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.10302168170611</v>
+        <v>7.166741023277243</v>
       </c>
       <c r="D10" t="n">
-        <v>4.744309684796041</v>
+        <v>0.7709503237793567</v>
       </c>
       <c r="E10" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F10" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.52536870319954</v>
+        <v>6.585372414269925</v>
       </c>
       <c r="D11" t="n">
-        <v>23.30314461199184</v>
+        <v>3.786760999448674</v>
       </c>
       <c r="E11" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F11" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.38887006536319</v>
+        <v>2.013191385621519</v>
       </c>
       <c r="D12" t="n">
-        <v>14.57842041088986</v>
+        <v>2.368993316769603</v>
       </c>
       <c r="E12" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F12" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.31763001844185</v>
+        <v>5.739114877996801</v>
       </c>
       <c r="D13" t="n">
-        <v>12.56981525459515</v>
+        <v>2.042594978871712</v>
       </c>
       <c r="E13" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F13" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.33293185316035</v>
+        <v>6.716601426138556</v>
       </c>
       <c r="D14" t="n">
-        <v>41.35784255417288</v>
+        <v>6.720649415053092</v>
       </c>
       <c r="E14" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F14" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.27999312917105</v>
+        <v>7.357998883490296</v>
       </c>
       <c r="D15" t="n">
-        <v>45.9380930835103</v>
+        <v>7.464940126070423</v>
       </c>
       <c r="E15" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F15" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.21969071516426</v>
+        <v>4.585699741214192</v>
       </c>
       <c r="D16" t="n">
-        <v>25.17935662402834</v>
+        <v>4.091645451404606</v>
       </c>
       <c r="E16" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F16" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>11.16704458900569</v>
+        <v>1.814644745713425</v>
       </c>
       <c r="D17" t="n">
-        <v>3.797200151327476</v>
+        <v>0.6170450245907148</v>
       </c>
       <c r="E17" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F17" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>6.943960882134864</v>
+        <v>1.128393643346915</v>
       </c>
       <c r="D18" t="n">
-        <v>10.16121928180643</v>
+        <v>1.651198133293545</v>
       </c>
       <c r="E18" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F18" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.30802605464732</v>
+        <v>7.85005423388019</v>
       </c>
       <c r="D19" t="n">
-        <v>46.96170595686522</v>
+        <v>7.631277217990598</v>
       </c>
       <c r="E19" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F19" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9.96341693502381</v>
+        <v>1.619055251941369</v>
       </c>
       <c r="D20" t="n">
-        <v>8.857310128628242</v>
+        <v>1.439312895902089</v>
       </c>
       <c r="E20" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F20" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>14.88707877562786</v>
+        <v>2.419150301039528</v>
       </c>
       <c r="D21" t="n">
-        <v>17.12029023378384</v>
+        <v>2.782047162989874</v>
       </c>
       <c r="E21" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F21" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>32.27703278580187</v>
+        <v>5.245017827692805</v>
       </c>
       <c r="D22" t="n">
-        <v>23.99511242559126</v>
+        <v>3.899205769158579</v>
       </c>
       <c r="E22" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F22" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>54.93743063947273</v>
+        <v>8.92733247891432</v>
       </c>
       <c r="D23" t="n">
-        <v>47.59535117353595</v>
+        <v>7.734244565699592</v>
       </c>
       <c r="E23" t="n">
-        <v>14.71198314990507</v>
+        <v>2.390697261859574</v>
       </c>
       <c r="F23" t="n">
-        <v>14.67085104714043</v>
+        <v>2.384013295160321</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
